--- a/bin/case.xlsx
+++ b/bin/case.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prg\GGRM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prg\GGRM\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="14">
   <si>
     <t>case_id</t>
   </si>
@@ -59,6 +59,18 @@
   <si>
     <t>status_</t>
   </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Settled</t>
+  </si>
+  <si>
+    <t>Denied</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
 </sst>
 </file>
 
@@ -66,7 +78,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -115,11 +127,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -881,56 +893,53 @@
       </c>
       <c r="C2">
         <f ca="1">VLOOKUP(M2, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>697</v>
+        <v>1407</v>
       </c>
       <c r="D2">
         <f ca="1">VLOOKUP(O2,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>1113</v>
+        <v>664</v>
       </c>
       <c r="E2" t="str">
         <f ca="1">IF(J2 &lt; 1, "Workers Compensation","Personal Injury")</f>
         <v>Personal Injury</v>
       </c>
-      <c r="F2" t="str">
-        <f ca="1">IF(K2 &lt; 1, "Open", IF(K2 &gt;= 2, "Settled", IF(K2 &gt;= 3, "Closed", "Denied")))</f>
-        <v>Settled</v>
+      <c r="F2" t="s">
+        <v>10</v>
       </c>
       <c r="G2" s="4">
         <v>44587</v>
       </c>
-      <c r="H2" s="4">
-        <v>45674</v>
-      </c>
+      <c r="H2" s="4"/>
       <c r="I2" s="2">
         <v>841298.25</v>
       </c>
       <c r="J2">
         <f ca="1">RAND()*2</f>
-        <v>1.8184012445869648</v>
+        <v>1.9565453868740283</v>
       </c>
       <c r="K2">
         <f ca="1">RAND()*4</f>
-        <v>3.3100317840807296</v>
+        <v>0.19260004251762242</v>
       </c>
       <c r="L2">
         <f ca="1">RAND()*25</f>
-        <v>18.846927584564252</v>
+        <v>4.8630499382715273</v>
       </c>
       <c r="M2">
         <f ca="1">ROUNDUP(L2, 0)</f>
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="N2">
         <f ca="1">RAND()*25</f>
-        <v>9.6911954375302791</v>
+        <v>8.8790238965296453</v>
       </c>
       <c r="O2">
         <f ca="1">ROUNDUP(N2, 0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P2" t="str">
         <f ca="1">CONCATENATE("(",B2,", ", C2, ", ", D2, ", ", CHAR(39), E2, CHAR(39), ", ", CHAR(39), F2, CHAR(39), ", ", CHAR(39), TEXT(G2, "yyyy-mm-dd"), CHAR(39), ", ", CHAR(39), TEXT(H2, "yyyy-mm-dd"), CHAR(39), ", ", I2,"),")</f>
-        <v>(222, 697, 1113, 'Personal Injury', 'Settled', '2022-01-26', '2025-01-17', 841298.25),</v>
+        <v>(222, 1407, 664, 'Personal Injury', 'Open', '2022-01-26', '1900-01-00', 841298.25),</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -942,56 +951,53 @@
       </c>
       <c r="C3">
         <f ca="1">VLOOKUP(M3, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>1467</v>
+        <v>212</v>
       </c>
       <c r="D3">
         <f ca="1">VLOOKUP(O3,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>1049</v>
+        <v>1575</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E26" ca="1" si="0">IF(J3 &lt; 1, "Workers Compensation","Personal Injury")</f>
         <v>Workers Compensation</v>
       </c>
-      <c r="F3" t="str">
-        <f t="shared" ref="F3:F26" ca="1" si="1">IF(K3 &lt; 1, "Open", IF(K3 &gt;= 2, "Settled", IF(K3 &gt;= 3, "Closed", "Denied")))</f>
-        <v>Open</v>
+      <c r="F3" t="s">
+        <v>10</v>
       </c>
       <c r="G3" s="4">
         <v>44651</v>
       </c>
-      <c r="H3" s="4">
-        <v>45679</v>
-      </c>
+      <c r="H3" s="4"/>
       <c r="I3" s="2">
         <v>240785.36</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J26" ca="1" si="2">RAND()*2</f>
-        <v>0.48566974731079138</v>
+        <f t="shared" ref="J3:J26" ca="1" si="1">RAND()*2</f>
+        <v>0.54423020519484488</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K26" ca="1" si="3">RAND()*4</f>
-        <v>8.9243998242718003E-2</v>
+        <f t="shared" ref="K3:K26" ca="1" si="2">RAND()*4</f>
+        <v>3.2676194310761861</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L26" ca="1" si="4">RAND()*25</f>
-        <v>17.20971203903342</v>
+        <f t="shared" ref="L3:L26" ca="1" si="3">RAND()*25</f>
+        <v>11.145650881275079</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M26" ca="1" si="5">ROUNDUP(L3, 0)</f>
-        <v>18</v>
+        <f t="shared" ref="M3:M26" ca="1" si="4">ROUNDUP(L3, 0)</f>
+        <v>12</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N26" ca="1" si="6">RAND()*25</f>
-        <v>13.473041534109154</v>
+        <f t="shared" ref="N3:N26" ca="1" si="5">RAND()*25</f>
+        <v>21.726664396049337</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O26" ca="1" si="7">ROUNDUP(N3, 0)</f>
-        <v>14</v>
+        <f t="shared" ref="O3:O26" ca="1" si="6">ROUNDUP(N3, 0)</f>
+        <v>22</v>
       </c>
       <c r="P3" t="str">
-        <f t="shared" ref="P3:P26" ca="1" si="8">CONCATENATE("(",B3,", ", C3, ", ", D3, ", ", CHAR(39), E3, CHAR(39), ", ", CHAR(39), F3, CHAR(39), ", ", CHAR(39), TEXT(G3, "yyyy-mm-dd"), CHAR(39), ", ", CHAR(39), TEXT(H3, "yyyy-mm-dd"), CHAR(39), ", ", I3,"),")</f>
-        <v>(1674, 1467, 1049, 'Workers Compensation', 'Open', '2022-03-31', '2025-01-22', 240785.36),</v>
+        <f t="shared" ref="P3:P26" ca="1" si="7">CONCATENATE("(",B3,", ", C3, ", ", D3, ", ", CHAR(39), E3, CHAR(39), ", ", CHAR(39), F3, CHAR(39), ", ", CHAR(39), TEXT(G3, "yyyy-mm-dd"), CHAR(39), ", ", CHAR(39), TEXT(H3, "yyyy-mm-dd"), CHAR(39), ", ", I3,"),")</f>
+        <v>(1674, 212, 1575, 'Workers Compensation', 'Open', '2022-03-31', '1900-01-00', 240785.36),</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -1003,19 +1009,18 @@
       </c>
       <c r="C4">
         <f ca="1">VLOOKUP(M4, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>1967</v>
+        <v>1258</v>
       </c>
       <c r="D4">
         <f ca="1">VLOOKUP(O4,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>1134</v>
+        <v>268</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Personal Injury</v>
-      </c>
-      <c r="F4" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Open</v>
+        <v>Workers Compensation</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
       </c>
       <c r="G4" s="4">
         <v>44655</v>
@@ -1027,32 +1032,32 @@
         <v>1118572.8500000001</v>
       </c>
       <c r="J4">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.65926735203963549</v>
+      </c>
+      <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>1.7488530284639598</v>
-      </c>
-      <c r="K4">
+        <v>2.7188144820426703</v>
+      </c>
+      <c r="L4">
         <f t="shared" ca="1" si="3"/>
-        <v>0.24547402797655682</v>
-      </c>
-      <c r="L4">
+        <v>5.4793131206071823</v>
+      </c>
+      <c r="M4">
         <f t="shared" ca="1" si="4"/>
-        <v>2.3537941173221997</v>
-      </c>
-      <c r="M4">
+        <v>6</v>
+      </c>
+      <c r="N4">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="N4">
+        <v>6.7658745386853711</v>
+      </c>
+      <c r="O4">
         <f t="shared" ca="1" si="6"/>
-        <v>1.6971769551961695</v>
-      </c>
-      <c r="O4">
+        <v>7</v>
+      </c>
+      <c r="P4" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="P4" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(638, 1967, 1134, 'Personal Injury', 'Open', '2022-04-04', '2025-01-31', 1118572.85),</v>
+        <v>(638, 1258, 268, 'Workers Compensation', 'Denied', '2022-04-04', '2025-01-31', 1118572.85),</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -1064,19 +1069,18 @@
       </c>
       <c r="C5">
         <f ca="1">VLOOKUP(M5, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>1576</v>
+        <v>913</v>
       </c>
       <c r="D5">
         <f ca="1">VLOOKUP(O5,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>1342</v>
+        <v>14</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Personal Injury</v>
       </c>
-      <c r="F5" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Settled</v>
+      <c r="F5" t="s">
+        <v>12</v>
       </c>
       <c r="G5" s="4">
         <v>44672</v>
@@ -1088,32 +1092,32 @@
         <v>1101815.23</v>
       </c>
       <c r="J5">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.8682193784787906</v>
+      </c>
+      <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>1.7151633901979386</v>
-      </c>
-      <c r="K5">
+        <v>0.8793830574931043</v>
+      </c>
+      <c r="L5">
         <f t="shared" ca="1" si="3"/>
-        <v>2.703288888918765</v>
-      </c>
-      <c r="L5">
+        <v>12.520270900828473</v>
+      </c>
+      <c r="M5">
         <f t="shared" ca="1" si="4"/>
-        <v>21.412554125761996</v>
-      </c>
-      <c r="M5">
+        <v>13</v>
+      </c>
+      <c r="N5">
         <f t="shared" ca="1" si="5"/>
-        <v>22</v>
-      </c>
-      <c r="N5">
+        <v>24.130691676076392</v>
+      </c>
+      <c r="O5">
         <f t="shared" ca="1" si="6"/>
-        <v>14.462584038128719</v>
-      </c>
-      <c r="O5">
+        <v>25</v>
+      </c>
+      <c r="P5" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="P5" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(804, 1576, 1342, 'Personal Injury', 'Settled', '2022-04-21', '2025-02-25', 1101815.23),</v>
+        <v>(804, 913, 14, 'Personal Injury', 'Denied', '2022-04-21', '2025-02-25', 1101815.23),</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -1125,19 +1129,18 @@
       </c>
       <c r="C6">
         <f ca="1">VLOOKUP(M6, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>332</v>
+        <v>195</v>
       </c>
       <c r="D6">
         <f ca="1">VLOOKUP(O6,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>268</v>
+        <v>14</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Personal Injury</v>
-      </c>
-      <c r="F6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Settled</v>
+        <v>Workers Compensation</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
       </c>
       <c r="G6" s="4">
         <v>44679</v>
@@ -1149,32 +1152,32 @@
         <v>258902.89</v>
       </c>
       <c r="J6">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.87514163324304262</v>
+      </c>
+      <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>1.8360890055248587</v>
-      </c>
-      <c r="K6">
+        <v>2.8602363270928546</v>
+      </c>
+      <c r="L6">
         <f t="shared" ca="1" si="3"/>
-        <v>3.2823387346326913</v>
-      </c>
-      <c r="L6">
+        <v>3.5598720761370881</v>
+      </c>
+      <c r="M6">
         <f t="shared" ca="1" si="4"/>
-        <v>13.753877182549157</v>
-      </c>
-      <c r="M6">
+        <v>4</v>
+      </c>
+      <c r="N6">
         <f t="shared" ca="1" si="5"/>
-        <v>14</v>
-      </c>
-      <c r="N6">
+        <v>24.872020313038252</v>
+      </c>
+      <c r="O6">
         <f t="shared" ca="1" si="6"/>
-        <v>6.630486601779884</v>
-      </c>
-      <c r="O6">
+        <v>25</v>
+      </c>
+      <c r="P6" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="P6" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(1896, 332, 268, 'Personal Injury', 'Settled', '2022-04-28', '', 258902.89),</v>
+        <v>(1896, 195, 14, 'Workers Compensation', 'Open', '2022-04-28', '', 258902.89),</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1186,19 +1189,18 @@
       </c>
       <c r="C7">
         <f ca="1">VLOOKUP(M7, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>91</v>
+        <v>1576</v>
       </c>
       <c r="D7">
         <f ca="1">VLOOKUP(O7,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>531</v>
+        <v>1859</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Personal Injury</v>
-      </c>
-      <c r="F7" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Settled</v>
+        <v>Workers Compensation</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
       </c>
       <c r="G7" s="4">
         <v>44701</v>
@@ -1210,32 +1212,32 @@
         <v>1216552.5</v>
       </c>
       <c r="J7">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.95427557148910336</v>
+      </c>
+      <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>1.0227919779897876</v>
-      </c>
-      <c r="K7">
+        <v>2.066613513353416</v>
+      </c>
+      <c r="L7">
         <f t="shared" ca="1" si="3"/>
-        <v>2.7457878957466906</v>
-      </c>
-      <c r="L7">
+        <v>21.009015792925258</v>
+      </c>
+      <c r="M7">
         <f t="shared" ca="1" si="4"/>
-        <v>24.469385630782099</v>
-      </c>
-      <c r="M7">
+        <v>22</v>
+      </c>
+      <c r="N7">
         <f t="shared" ca="1" si="5"/>
-        <v>25</v>
-      </c>
-      <c r="N7">
+        <v>16.164456195414598</v>
+      </c>
+      <c r="O7">
         <f t="shared" ca="1" si="6"/>
-        <v>17.185661274339591</v>
-      </c>
-      <c r="O7">
+        <v>17</v>
+      </c>
+      <c r="P7" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>18</v>
-      </c>
-      <c r="P7" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(548, 91, 531, 'Personal Injury', 'Settled', '2022-05-20', '', 1216552.5),</v>
+        <v>(548, 1576, 1859, 'Workers Compensation', 'Open', '2022-05-20', '', 1216552.5),</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -1247,19 +1249,18 @@
       </c>
       <c r="C8">
         <f ca="1">VLOOKUP(M8, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>941</v>
+        <v>1407</v>
       </c>
       <c r="D8">
         <f ca="1">VLOOKUP(O8,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>14</v>
+        <v>1727</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Personal Injury</v>
       </c>
-      <c r="F8" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Settled</v>
+      <c r="F8" t="s">
+        <v>11</v>
       </c>
       <c r="G8" s="4">
         <v>44852</v>
@@ -1271,32 +1272,32 @@
         <v>1188711.95</v>
       </c>
       <c r="J8">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.0670311828101859</v>
+      </c>
+      <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>1.6908086532837761</v>
-      </c>
-      <c r="K8">
+        <v>1.2345543735426427</v>
+      </c>
+      <c r="L8">
         <f t="shared" ca="1" si="3"/>
-        <v>3.6885872708635303</v>
-      </c>
-      <c r="L8">
+        <v>4.7625439992379865</v>
+      </c>
+      <c r="M8">
         <f t="shared" ca="1" si="4"/>
-        <v>23.153219459477771</v>
-      </c>
-      <c r="M8">
+        <v>5</v>
+      </c>
+      <c r="N8">
         <f t="shared" ca="1" si="5"/>
-        <v>24</v>
-      </c>
-      <c r="N8">
+        <v>11.004105956602029</v>
+      </c>
+      <c r="O8">
         <f t="shared" ca="1" si="6"/>
-        <v>24.868980742831976</v>
-      </c>
-      <c r="O8">
+        <v>12</v>
+      </c>
+      <c r="P8" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>25</v>
-      </c>
-      <c r="P8" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(1401, 941, 14, 'Personal Injury', 'Settled', '2022-10-18', '2025-03-21', 1188711.95),</v>
+        <v>(1401, 1407, 1727, 'Personal Injury', 'Settled', '2022-10-18', '2025-03-21', 1188711.95),</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1308,19 +1309,18 @@
       </c>
       <c r="C9">
         <f ca="1">VLOOKUP(M9, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>1467</v>
+        <v>1967</v>
       </c>
       <c r="D9">
         <f ca="1">VLOOKUP(O9,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>931</v>
+        <v>1740</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Personal Injury</v>
-      </c>
-      <c r="F9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Denied</v>
+        <v>Workers Compensation</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
       </c>
       <c r="G9" s="4">
         <v>44900</v>
@@ -1332,32 +1332,32 @@
         <v>424776.96000000002</v>
       </c>
       <c r="J9">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.97738711872764661</v>
+      </c>
+      <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>1.2604456340406229</v>
-      </c>
-      <c r="K9">
+        <v>0.89951227472268336</v>
+      </c>
+      <c r="L9">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5824726139835206</v>
-      </c>
-      <c r="L9">
+        <v>2.7967039001053684</v>
+      </c>
+      <c r="M9">
         <f t="shared" ca="1" si="4"/>
-        <v>17.913116024411675</v>
-      </c>
-      <c r="M9">
+        <v>3</v>
+      </c>
+      <c r="N9">
         <f t="shared" ca="1" si="5"/>
-        <v>18</v>
-      </c>
-      <c r="N9">
+        <v>15.746332074755031</v>
+      </c>
+      <c r="O9">
         <f t="shared" ca="1" si="6"/>
-        <v>10.952514554441864</v>
-      </c>
-      <c r="O9">
+        <v>16</v>
+      </c>
+      <c r="P9" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>11</v>
-      </c>
-      <c r="P9" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(1341, 1467, 931, 'Personal Injury', 'Denied', '2022-12-05', '2025-03-28', 424776.96),</v>
+        <v>(1341, 1967, 1740, 'Workers Compensation', 'Settled', '2022-12-05', '2025-03-28', 424776.96),</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C10">
         <f ca="1">VLOOKUP(M10, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>913</v>
+        <v>1834</v>
       </c>
       <c r="D10">
         <f ca="1">VLOOKUP(O10,[2]attorney!$A$2:$B$26,2,FALSE)</f>
@@ -1379,9 +1379,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>Workers Compensation</v>
       </c>
-      <c r="F10" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Denied</v>
+      <c r="F10" t="s">
+        <v>11</v>
       </c>
       <c r="G10" s="4">
         <v>44929</v>
@@ -1393,32 +1392,32 @@
         <v>1161940.8600000001</v>
       </c>
       <c r="J10">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.59320792277305023</v>
+      </c>
+      <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>0.64320133996371842</v>
-      </c>
-      <c r="K10">
+        <v>9.6312301912476972E-2</v>
+      </c>
+      <c r="L10">
         <f t="shared" ca="1" si="3"/>
-        <v>1.45149319166832</v>
-      </c>
-      <c r="L10">
+        <v>7.6507817490934773</v>
+      </c>
+      <c r="M10">
         <f t="shared" ca="1" si="4"/>
-        <v>12.865203114278339</v>
-      </c>
-      <c r="M10">
+        <v>8</v>
+      </c>
+      <c r="N10">
         <f t="shared" ca="1" si="5"/>
-        <v>13</v>
-      </c>
-      <c r="N10">
+        <v>9.6367893519324426</v>
+      </c>
+      <c r="O10">
         <f t="shared" ca="1" si="6"/>
-        <v>9.8054861399799265</v>
-      </c>
-      <c r="O10">
+        <v>10</v>
+      </c>
+      <c r="P10" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="P10" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(1992, 913, 1113, 'Workers Compensation', 'Denied', '2023-01-03', '2025-04-24', 1161940.86),</v>
+        <v>(1992, 1834, 1113, 'Workers Compensation', 'Settled', '2023-01-03', '2025-04-24', 1161940.86),</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1430,19 +1429,18 @@
       </c>
       <c r="C11">
         <f ca="1">VLOOKUP(M11, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>195</v>
+        <v>740</v>
       </c>
       <c r="D11">
         <f ca="1">VLOOKUP(O11,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>517</v>
+        <v>1238</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Personal Injury</v>
-      </c>
-      <c r="F11" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Open</v>
+        <v>Workers Compensation</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
       </c>
       <c r="G11" s="4">
         <v>44966</v>
@@ -1454,32 +1452,32 @@
         <v>618423.48</v>
       </c>
       <c r="J11">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.77068667246136324</v>
+      </c>
+      <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>1.9545793767123802</v>
-      </c>
-      <c r="K11">
+        <v>1.4472151512026286</v>
+      </c>
+      <c r="L11">
         <f t="shared" ca="1" si="3"/>
-        <v>0.60095076831262162</v>
-      </c>
-      <c r="L11">
+        <v>15.398390192874867</v>
+      </c>
+      <c r="M11">
         <f t="shared" ca="1" si="4"/>
-        <v>3.3852505000858097</v>
-      </c>
-      <c r="M11">
+        <v>16</v>
+      </c>
+      <c r="N11">
         <f t="shared" ca="1" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="N11">
+        <v>19.920612267208028</v>
+      </c>
+      <c r="O11">
         <f t="shared" ca="1" si="6"/>
-        <v>5.7715436540935503</v>
-      </c>
-      <c r="O11">
+        <v>20</v>
+      </c>
+      <c r="P11" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="P11" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(346, 195, 517, 'Personal Injury', 'Open', '2023-02-09', '2025-05-02', 618423.48),</v>
+        <v>(346, 740, 1238, 'Workers Compensation', 'Settled', '2023-02-09', '2025-05-02', 618423.48),</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1491,19 +1489,18 @@
       </c>
       <c r="C12">
         <f ca="1">VLOOKUP(M12, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>861</v>
+        <v>740</v>
       </c>
       <c r="D12">
         <f ca="1">VLOOKUP(O12,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>1054</v>
+        <v>625</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Workers Compensation</v>
-      </c>
-      <c r="F12" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Open</v>
+        <v>Personal Injury</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
       </c>
       <c r="G12" s="4">
         <v>44980</v>
@@ -1515,32 +1512,32 @@
         <v>1128266.8</v>
       </c>
       <c r="J12">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.6931681401030947</v>
+      </c>
+      <c r="K12">
         <f t="shared" ca="1" si="2"/>
-        <v>0.67974436572972818</v>
-      </c>
-      <c r="K12">
+        <v>1.4223732657195209</v>
+      </c>
+      <c r="L12">
         <f t="shared" ca="1" si="3"/>
-        <v>1.6410234435208615E-2</v>
-      </c>
-      <c r="L12">
+        <v>15.244222840221028</v>
+      </c>
+      <c r="M12">
         <f t="shared" ca="1" si="4"/>
-        <v>10.113233852339478</v>
-      </c>
-      <c r="M12">
+        <v>16</v>
+      </c>
+      <c r="N12">
         <f t="shared" ca="1" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="N12">
+        <v>2.1431684762474976</v>
+      </c>
+      <c r="O12">
         <f t="shared" ca="1" si="6"/>
-        <v>0.34085899467938552</v>
-      </c>
-      <c r="O12">
+        <v>3</v>
+      </c>
+      <c r="P12" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="P12" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(1884, 861, 1054, 'Workers Compensation', 'Open', '2023-02-23', '2025-05-21', 1128266.8),</v>
+        <v>(1884, 740, 625, 'Personal Injury', 'Settled', '2023-02-23', '2025-05-21', 1128266.8),</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1552,19 +1549,18 @@
       </c>
       <c r="C13">
         <f ca="1">VLOOKUP(M13, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>1126</v>
+        <v>332</v>
       </c>
       <c r="D13">
         <f ca="1">VLOOKUP(O13,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>1422</v>
+        <v>1575</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Personal Injury</v>
       </c>
-      <c r="F13" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Settled</v>
+      <c r="F13" t="s">
+        <v>10</v>
       </c>
       <c r="G13" s="4">
         <v>45114</v>
@@ -1576,32 +1572,32 @@
         <v>171852.49</v>
       </c>
       <c r="J13">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.441942826369192</v>
+      </c>
+      <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>1.7057782045877314</v>
-      </c>
-      <c r="K13">
+        <v>1.8178428705184757</v>
+      </c>
+      <c r="L13">
         <f t="shared" ca="1" si="3"/>
-        <v>3.3054396782153224</v>
-      </c>
-      <c r="L13">
+        <v>13.657987019419386</v>
+      </c>
+      <c r="M13">
         <f t="shared" ca="1" si="4"/>
-        <v>19.636276060427999</v>
-      </c>
-      <c r="M13">
+        <v>14</v>
+      </c>
+      <c r="N13">
         <f t="shared" ca="1" si="5"/>
-        <v>20</v>
-      </c>
-      <c r="N13">
+        <v>21.654125622192414</v>
+      </c>
+      <c r="O13">
         <f t="shared" ca="1" si="6"/>
-        <v>4.8461811733417264</v>
-      </c>
-      <c r="O13">
+        <v>22</v>
+      </c>
+      <c r="P13" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="P13" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(92, 1126, 1422, 'Personal Injury', 'Settled', '2023-07-07', '', 171852.49),</v>
+        <v>(92, 332, 1575, 'Personal Injury', 'Open', '2023-07-07', '', 171852.49),</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1623,9 +1619,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>Workers Compensation</v>
       </c>
-      <c r="F14" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Denied</v>
+      <c r="F14" t="s">
+        <v>10</v>
       </c>
       <c r="G14" s="4">
         <v>45152</v>
@@ -1637,32 +1632,32 @@
         <v>1095853.76</v>
       </c>
       <c r="J14">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.84675386026711674</v>
+      </c>
+      <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>0.52985724014709579</v>
-      </c>
-      <c r="K14">
+        <v>2.8821818925925697</v>
+      </c>
+      <c r="L14">
         <f t="shared" ca="1" si="3"/>
-        <v>1.9636083063955296</v>
-      </c>
-      <c r="L14">
+        <v>21.340600883086534</v>
+      </c>
+      <c r="M14">
         <f t="shared" ca="1" si="4"/>
-        <v>21.465888993049091</v>
-      </c>
-      <c r="M14">
+        <v>22</v>
+      </c>
+      <c r="N14">
         <f t="shared" ca="1" si="5"/>
-        <v>22</v>
-      </c>
-      <c r="N14">
+        <v>14.282848179862043</v>
+      </c>
+      <c r="O14">
         <f t="shared" ca="1" si="6"/>
-        <v>14.8072040349057</v>
-      </c>
-      <c r="O14">
+        <v>15</v>
+      </c>
+      <c r="P14" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="P14" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(717, 1576, 1342, 'Workers Compensation', 'Denied', '2023-08-14', '', 1095853.76),</v>
+        <v>(717, 1576, 1342, 'Workers Compensation', 'Open', '2023-08-14', '', 1095853.76),</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1674,19 +1669,18 @@
       </c>
       <c r="C15">
         <f ca="1">VLOOKUP(M15, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>1048</v>
+        <v>1407</v>
       </c>
       <c r="D15">
         <f ca="1">VLOOKUP(O15,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>1575</v>
+        <v>249</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Personal Injury</v>
       </c>
-      <c r="F15" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Settled</v>
+      <c r="F15" t="s">
+        <v>10</v>
       </c>
       <c r="G15" s="4">
         <v>45219</v>
@@ -1698,32 +1692,32 @@
         <v>1262767.19</v>
       </c>
       <c r="J15">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.3613466320050975</v>
+      </c>
+      <c r="K15">
         <f t="shared" ca="1" si="2"/>
-        <v>1.5108151865166275</v>
-      </c>
-      <c r="K15">
+        <v>2.4449126907078713</v>
+      </c>
+      <c r="L15">
         <f t="shared" ca="1" si="3"/>
-        <v>2.4500886055281139</v>
-      </c>
-      <c r="L15">
+        <v>4.0898222393588091</v>
+      </c>
+      <c r="M15">
         <f t="shared" ca="1" si="4"/>
-        <v>1.8997071695583179</v>
-      </c>
-      <c r="M15">
+        <v>5</v>
+      </c>
+      <c r="N15">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="N15">
+        <v>20.014800812632576</v>
+      </c>
+      <c r="O15">
         <f t="shared" ca="1" si="6"/>
-        <v>21.457175849504459</v>
-      </c>
-      <c r="O15">
+        <v>21</v>
+      </c>
+      <c r="P15" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>22</v>
-      </c>
-      <c r="P15" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(1520, 1048, 1575, 'Personal Injury', 'Settled', '2023-10-20', '', 1262767.19),</v>
+        <v>(1520, 1407, 249, 'Personal Injury', 'Open', '2023-10-20', '', 1262767.19),</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1735,19 +1729,18 @@
       </c>
       <c r="C16">
         <f ca="1">VLOOKUP(M16, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>284</v>
+        <v>1126</v>
       </c>
       <c r="D16">
         <f ca="1">VLOOKUP(O16,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>1238</v>
+        <v>664</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Workers Compensation</v>
       </c>
-      <c r="F16" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Settled</v>
+      <c r="F16" t="s">
+        <v>10</v>
       </c>
       <c r="G16" s="4">
         <v>45334</v>
@@ -1759,32 +1752,32 @@
         <v>1097620.1000000001</v>
       </c>
       <c r="J16">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.61449556643973025</v>
+      </c>
+      <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>0.65070453194624012</v>
-      </c>
-      <c r="K16">
+        <v>1.3913235063122387</v>
+      </c>
+      <c r="L16">
         <f t="shared" ca="1" si="3"/>
-        <v>3.6728379597683931</v>
-      </c>
-      <c r="L16">
+        <v>19.646338845898409</v>
+      </c>
+      <c r="M16">
         <f t="shared" ca="1" si="4"/>
-        <v>14.596373544553193</v>
-      </c>
-      <c r="M16">
+        <v>20</v>
+      </c>
+      <c r="N16">
         <f t="shared" ca="1" si="5"/>
-        <v>15</v>
-      </c>
-      <c r="N16">
+        <v>8.6265507010466731</v>
+      </c>
+      <c r="O16">
         <f t="shared" ca="1" si="6"/>
-        <v>19.066112097718541</v>
-      </c>
-      <c r="O16">
+        <v>9</v>
+      </c>
+      <c r="P16" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="P16" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(83, 284, 1238, 'Workers Compensation', 'Settled', '2024-02-12', '', 1097620.1),</v>
+        <v>(83, 1126, 664, 'Workers Compensation', 'Open', '2024-02-12', '', 1097620.1),</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1800,15 +1793,14 @@
       </c>
       <c r="D17">
         <f ca="1">VLOOKUP(O17,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>1113</v>
+        <v>503</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Personal Injury</v>
       </c>
-      <c r="F17" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Settled</v>
+      <c r="F17" t="s">
+        <v>13</v>
       </c>
       <c r="G17" s="4">
         <v>45406</v>
@@ -1820,32 +1812,32 @@
         <v>492574.75</v>
       </c>
       <c r="J17">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.6052303339252867</v>
+      </c>
+      <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>1.1115972535867285</v>
-      </c>
-      <c r="K17">
+        <v>2.9510868804292558</v>
+      </c>
+      <c r="L17">
         <f t="shared" ca="1" si="3"/>
-        <v>2.8976255746954438</v>
-      </c>
-      <c r="L17">
+        <v>23.587348168813012</v>
+      </c>
+      <c r="M17">
         <f t="shared" ca="1" si="4"/>
-        <v>23.942315144198034</v>
-      </c>
-      <c r="M17">
+        <v>24</v>
+      </c>
+      <c r="N17">
         <f t="shared" ca="1" si="5"/>
+        <v>23.870578437839733</v>
+      </c>
+      <c r="O17">
+        <f t="shared" ca="1" si="6"/>
         <v>24</v>
       </c>
-      <c r="N17">
-        <f t="shared" ca="1" si="6"/>
-        <v>9.3044894652301586</v>
-      </c>
-      <c r="O17">
+      <c r="P17" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="P17" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(1900, 941, 1113, 'Personal Injury', 'Settled', '2024-04-24', '2025-08-06', 492574.75),</v>
+        <v>(1900, 941, 503, 'Personal Injury', 'Closed', '2024-04-24', '2025-08-06', 492574.75),</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1857,7 +1849,7 @@
       </c>
       <c r="C18">
         <f ca="1">VLOOKUP(M18, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>941</v>
+        <v>53</v>
       </c>
       <c r="D18">
         <f ca="1">VLOOKUP(O18,[2]attorney!$A$2:$B$26,2,FALSE)</f>
@@ -1865,11 +1857,10 @@
       </c>
       <c r="E18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Workers Compensation</v>
-      </c>
-      <c r="F18" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Settled</v>
+        <v>Personal Injury</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
       </c>
       <c r="G18" s="4">
         <v>45429</v>
@@ -1881,32 +1872,32 @@
         <v>651054.77</v>
       </c>
       <c r="J18">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.4962936799418423</v>
+      </c>
+      <c r="K18">
         <f t="shared" ca="1" si="2"/>
-        <v>0.72599464727180774</v>
-      </c>
-      <c r="K18">
+        <v>1.724342197706588</v>
+      </c>
+      <c r="L18">
         <f t="shared" ca="1" si="3"/>
-        <v>3.3897803632946015</v>
-      </c>
-      <c r="L18">
+        <v>16.023567011326008</v>
+      </c>
+      <c r="M18">
         <f t="shared" ca="1" si="4"/>
-        <v>23.32726949315299</v>
-      </c>
-      <c r="M18">
+        <v>17</v>
+      </c>
+      <c r="N18">
         <f t="shared" ca="1" si="5"/>
-        <v>24</v>
-      </c>
-      <c r="N18">
+        <v>12.72235564673054</v>
+      </c>
+      <c r="O18">
         <f t="shared" ca="1" si="6"/>
-        <v>12.839477675746206</v>
-      </c>
-      <c r="O18">
+        <v>13</v>
+      </c>
+      <c r="P18" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>13</v>
-      </c>
-      <c r="P18" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(1343, 941, 901, 'Workers Compensation', 'Settled', '2024-05-17', '2025-08-08', 651054.77),</v>
+        <v>(1343, 53, 901, 'Personal Injury', 'Closed', '2024-05-17', '2025-08-08', 651054.77),</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -1918,19 +1909,18 @@
       </c>
       <c r="C19">
         <f ca="1">VLOOKUP(M19, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>861</v>
+        <v>1576</v>
       </c>
       <c r="D19">
         <f ca="1">VLOOKUP(O19,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>249</v>
+        <v>1859</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Workers Compensation</v>
-      </c>
-      <c r="F19" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Settled</v>
+        <v>Personal Injury</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
       </c>
       <c r="G19" s="4">
         <v>45454</v>
@@ -1942,32 +1932,32 @@
         <v>1011605.82</v>
       </c>
       <c r="J19">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.1895573849763541</v>
+      </c>
+      <c r="K19">
         <f t="shared" ca="1" si="2"/>
-        <v>0.35889145070949069</v>
-      </c>
-      <c r="K19">
+        <v>3.9479495790459715</v>
+      </c>
+      <c r="L19">
         <f t="shared" ca="1" si="3"/>
-        <v>3.9118076621749549</v>
-      </c>
-      <c r="L19">
+        <v>21.56999052822723</v>
+      </c>
+      <c r="M19">
         <f t="shared" ca="1" si="4"/>
-        <v>10.839591179788584</v>
-      </c>
-      <c r="M19">
+        <v>22</v>
+      </c>
+      <c r="N19">
         <f t="shared" ca="1" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="N19">
+        <v>16.54990932286486</v>
+      </c>
+      <c r="O19">
         <f t="shared" ca="1" si="6"/>
-        <v>20.760090929924814</v>
-      </c>
-      <c r="O19">
+        <v>17</v>
+      </c>
+      <c r="P19" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>21</v>
-      </c>
-      <c r="P19" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(50, 861, 249, 'Workers Compensation', 'Settled', '2024-06-11', '2025-11-07', 1011605.82),</v>
+        <v>(50, 1576, 1859, 'Personal Injury', 'Closed', '2024-06-11', '2025-11-07', 1011605.82),</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -1983,15 +1973,14 @@
       </c>
       <c r="D20">
         <f ca="1">VLOOKUP(O20,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>1342</v>
+        <v>268</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Workers Compensation</v>
       </c>
-      <c r="F20" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Settled</v>
+      <c r="F20" t="s">
+        <v>13</v>
       </c>
       <c r="G20" s="4">
         <v>45461</v>
@@ -2003,32 +1992,32 @@
         <v>771049.59</v>
       </c>
       <c r="J20">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.77851045673911856</v>
+      </c>
+      <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>0.3296780747518544</v>
-      </c>
-      <c r="K20">
+        <v>2.200134735863899</v>
+      </c>
+      <c r="L20">
         <f t="shared" ca="1" si="3"/>
-        <v>2.1300610943161442</v>
-      </c>
-      <c r="L20">
+        <v>24.313369301428121</v>
+      </c>
+      <c r="M20">
         <f t="shared" ca="1" si="4"/>
-        <v>24.327630742319268</v>
-      </c>
-      <c r="M20">
+        <v>25</v>
+      </c>
+      <c r="N20">
         <f t="shared" ca="1" si="5"/>
-        <v>25</v>
-      </c>
-      <c r="N20">
+        <v>6.8209478614340018</v>
+      </c>
+      <c r="O20">
         <f t="shared" ca="1" si="6"/>
-        <v>14.74334731693116</v>
-      </c>
-      <c r="O20">
+        <v>7</v>
+      </c>
+      <c r="P20" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>15</v>
-      </c>
-      <c r="P20" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(723, 91, 1342, 'Workers Compensation', 'Settled', '2024-06-18', '2025-12-05', 771049.59),</v>
+        <v>(723, 91, 268, 'Workers Compensation', 'Closed', '2024-06-18', '2025-12-05', 771049.59),</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -2040,19 +2029,18 @@
       </c>
       <c r="C21">
         <f ca="1">VLOOKUP(M21, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>1754</v>
+        <v>941</v>
       </c>
       <c r="D21">
         <f ca="1">VLOOKUP(O21,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>753</v>
+        <v>503</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Personal Injury</v>
       </c>
-      <c r="F21" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Settled</v>
+      <c r="F21" t="s">
+        <v>13</v>
       </c>
       <c r="G21" s="4">
         <v>45476</v>
@@ -2064,32 +2052,32 @@
         <v>788680.14</v>
       </c>
       <c r="J21">
+        <f t="shared" ca="1" si="1"/>
+        <v>1.2331727193493813</v>
+      </c>
+      <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>1.7817997029449664</v>
-      </c>
-      <c r="K21">
+        <v>3.1794732833772708</v>
+      </c>
+      <c r="L21">
         <f t="shared" ca="1" si="3"/>
-        <v>3.8100760174909793</v>
-      </c>
-      <c r="L21">
+        <v>23.224110817551232</v>
+      </c>
+      <c r="M21">
         <f t="shared" ca="1" si="4"/>
-        <v>6.831891124595046</v>
-      </c>
-      <c r="M21">
+        <v>24</v>
+      </c>
+      <c r="N21">
         <f t="shared" ca="1" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="N21">
+        <v>23.288697492563248</v>
+      </c>
+      <c r="O21">
         <f t="shared" ca="1" si="6"/>
-        <v>18.2276195110936</v>
-      </c>
-      <c r="O21">
+        <v>24</v>
+      </c>
+      <c r="P21" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>19</v>
-      </c>
-      <c r="P21" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(1773, 1754, 753, 'Personal Injury', 'Settled', '2024-07-03', '2025-12-31', 788680.14),</v>
+        <v>(1773, 941, 503, 'Personal Injury', 'Closed', '2024-07-03', '2025-12-31', 788680.14),</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -2101,19 +2089,18 @@
       </c>
       <c r="C22">
         <f ca="1">VLOOKUP(M22, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>1048</v>
+        <v>466</v>
       </c>
       <c r="D22">
         <f ca="1">VLOOKUP(O22,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>249</v>
+        <v>663</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Personal Injury</v>
-      </c>
-      <c r="F22" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Open</v>
+        <v>Workers Compensation</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
       </c>
       <c r="G22" s="4">
         <v>45519</v>
@@ -2125,32 +2112,32 @@
         <v>378269.52</v>
       </c>
       <c r="J22">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.73169173788482489</v>
+      </c>
+      <c r="K22">
         <f t="shared" ca="1" si="2"/>
-        <v>1.2259709922631159</v>
-      </c>
-      <c r="K22">
+        <v>3.910731441097326E-2</v>
+      </c>
+      <c r="L22">
         <f t="shared" ca="1" si="3"/>
-        <v>0.16323702073305801</v>
-      </c>
-      <c r="L22">
+        <v>8.1975796594422423</v>
+      </c>
+      <c r="M22">
         <f t="shared" ca="1" si="4"/>
-        <v>1.3606663034790634</v>
-      </c>
-      <c r="M22">
+        <v>9</v>
+      </c>
+      <c r="N22">
         <f t="shared" ca="1" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="N22">
+        <v>7.0361399428479272</v>
+      </c>
+      <c r="O22">
         <f t="shared" ca="1" si="6"/>
-        <v>20.816518618496236</v>
-      </c>
-      <c r="O22">
+        <v>8</v>
+      </c>
+      <c r="P22" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>21</v>
-      </c>
-      <c r="P22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(1079, 1048, 249, 'Personal Injury', 'Open', '2024-08-15', '', 378269.52),</v>
+        <v>(1079, 466, 663, 'Workers Compensation', 'Open', '2024-08-15', '', 378269.52),</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -2162,19 +2149,18 @@
       </c>
       <c r="C23">
         <f ca="1">VLOOKUP(M23, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>1754</v>
+        <v>1258</v>
       </c>
       <c r="D23">
         <f ca="1">VLOOKUP(O23,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>14</v>
+        <v>664</v>
       </c>
       <c r="E23" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Workers Compensation</v>
       </c>
-      <c r="F23" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Settled</v>
+      <c r="F23" t="s">
+        <v>10</v>
       </c>
       <c r="G23" s="4">
         <v>45552</v>
@@ -2186,32 +2172,32 @@
         <v>395642.57</v>
       </c>
       <c r="J23">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.55288007710937359</v>
+      </c>
+      <c r="K23">
         <f t="shared" ca="1" si="2"/>
-        <v>2.3226145089763284E-2</v>
-      </c>
-      <c r="K23">
+        <v>2.1754333972322417</v>
+      </c>
+      <c r="L23">
         <f t="shared" ca="1" si="3"/>
-        <v>3.7172122614184011</v>
-      </c>
-      <c r="L23">
+        <v>5.0154301302875988</v>
+      </c>
+      <c r="M23">
         <f t="shared" ca="1" si="4"/>
-        <v>6.390435410055642</v>
-      </c>
-      <c r="M23">
+        <v>6</v>
+      </c>
+      <c r="N23">
         <f t="shared" ca="1" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="N23">
+        <v>8.9309125202581239</v>
+      </c>
+      <c r="O23">
         <f t="shared" ca="1" si="6"/>
-        <v>24.453147628174026</v>
-      </c>
-      <c r="O23">
+        <v>9</v>
+      </c>
+      <c r="P23" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>25</v>
-      </c>
-      <c r="P23" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(123, 1754, 14, 'Workers Compensation', 'Settled', '2024-09-17', '', 395642.57),</v>
+        <v>(123, 1258, 664, 'Workers Compensation', 'Open', '2024-09-17', '', 395642.57),</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -2223,19 +2209,18 @@
       </c>
       <c r="C24">
         <f ca="1">VLOOKUP(M24, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>1048</v>
+        <v>1467</v>
       </c>
       <c r="D24">
         <f ca="1">VLOOKUP(O24,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>1568</v>
+        <v>1134</v>
       </c>
       <c r="E24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Personal Injury</v>
-      </c>
-      <c r="F24" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Settled</v>
+        <v>Workers Compensation</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
       </c>
       <c r="G24" s="4">
         <v>45597</v>
@@ -2247,32 +2232,32 @@
         <v>963773.63</v>
       </c>
       <c r="J24">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.1409278716541762</v>
+      </c>
+      <c r="K24">
         <f t="shared" ca="1" si="2"/>
-        <v>1.314261872652482</v>
-      </c>
-      <c r="K24">
+        <v>3.2928964276375345</v>
+      </c>
+      <c r="L24">
         <f t="shared" ca="1" si="3"/>
-        <v>2.4265455291227775</v>
-      </c>
-      <c r="L24">
+        <v>17.764506885642771</v>
+      </c>
+      <c r="M24">
         <f t="shared" ca="1" si="4"/>
-        <v>1.2837851643545783</v>
-      </c>
-      <c r="M24">
+        <v>18</v>
+      </c>
+      <c r="N24">
         <f t="shared" ca="1" si="5"/>
+        <v>1.8797239644937791</v>
+      </c>
+      <c r="O24">
+        <f t="shared" ca="1" si="6"/>
         <v>2</v>
       </c>
-      <c r="N24">
-        <f t="shared" ca="1" si="6"/>
-        <v>3.0322315776783624</v>
-      </c>
-      <c r="O24">
+      <c r="P24" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="P24" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(1091, 1048, 1568, 'Personal Injury', 'Settled', '2024-11-01', '2026-02-11', 963773.63),</v>
+        <v>(1091, 1467, 1134, 'Workers Compensation', 'Closed', '2024-11-01', '2026-02-11', 963773.63),</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -2284,19 +2269,18 @@
       </c>
       <c r="C25">
         <f ca="1">VLOOKUP(M25, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>466</v>
+        <v>1258</v>
       </c>
       <c r="D25">
         <f ca="1">VLOOKUP(O25,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>249</v>
+        <v>1766</v>
       </c>
       <c r="E25" t="str">
         <f t="shared" ca="1" si="0"/>
         <v>Workers Compensation</v>
       </c>
-      <c r="F25" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Denied</v>
+      <c r="F25" t="s">
+        <v>10</v>
       </c>
       <c r="G25" s="4">
         <v>45621</v>
@@ -2308,32 +2292,32 @@
         <v>946378.56</v>
       </c>
       <c r="J25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.54375047316846903</v>
+      </c>
+      <c r="K25">
         <f t="shared" ca="1" si="2"/>
-        <v>0.45578460572005164</v>
-      </c>
-      <c r="K25">
+        <v>2.1458419420507222</v>
+      </c>
+      <c r="L25">
         <f t="shared" ca="1" si="3"/>
-        <v>1.3052955251502403</v>
-      </c>
-      <c r="L25">
+        <v>5.1347056588551574</v>
+      </c>
+      <c r="M25">
         <f t="shared" ca="1" si="4"/>
-        <v>8.0300006350653899</v>
-      </c>
-      <c r="M25">
+        <v>6</v>
+      </c>
+      <c r="N25">
         <f t="shared" ca="1" si="5"/>
-        <v>9</v>
-      </c>
-      <c r="N25">
+        <v>22.818799207848233</v>
+      </c>
+      <c r="O25">
         <f t="shared" ca="1" si="6"/>
-        <v>20.342314608127239</v>
-      </c>
-      <c r="O25">
+        <v>23</v>
+      </c>
+      <c r="P25" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>21</v>
-      </c>
-      <c r="P25" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(1538, 466, 249, 'Workers Compensation', 'Denied', '2024-11-25', '', 946378.56),</v>
+        <v>(1538, 1258, 1766, 'Workers Compensation', 'Open', '2024-11-25', '', 946378.56),</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -2345,19 +2329,18 @@
       </c>
       <c r="C26">
         <f ca="1">VLOOKUP(M26, [1]client!$A$2:$B$26,2, FALSE)</f>
-        <v>697</v>
+        <v>53</v>
       </c>
       <c r="D26">
         <f ca="1">VLOOKUP(O26,[2]attorney!$A$2:$B$26,2,FALSE)</f>
-        <v>14</v>
+        <v>1422</v>
       </c>
       <c r="E26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Personal Injury</v>
-      </c>
-      <c r="F26" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Open</v>
+        <v>Workers Compensation</v>
+      </c>
+      <c r="F26" t="s">
+        <v>10</v>
       </c>
       <c r="G26" s="4">
         <v>45622</v>
@@ -2369,32 +2352,32 @@
         <v>462835.94</v>
       </c>
       <c r="J26">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.20222916754299791</v>
+      </c>
+      <c r="K26">
         <f t="shared" ca="1" si="2"/>
-        <v>1.0393444068775868</v>
-      </c>
-      <c r="K26">
+        <v>3.4272056093529759</v>
+      </c>
+      <c r="L26">
         <f t="shared" ca="1" si="3"/>
-        <v>0.13409973287876165</v>
-      </c>
-      <c r="L26">
+        <v>16.123600136748788</v>
+      </c>
+      <c r="M26">
         <f t="shared" ca="1" si="4"/>
-        <v>18.220677582398999</v>
-      </c>
-      <c r="M26">
+        <v>17</v>
+      </c>
+      <c r="N26">
         <f t="shared" ca="1" si="5"/>
-        <v>19</v>
-      </c>
-      <c r="N26">
+        <v>4.3459423072903789</v>
+      </c>
+      <c r="O26">
         <f t="shared" ca="1" si="6"/>
-        <v>24.777090854586344</v>
-      </c>
-      <c r="O26">
+        <v>5</v>
+      </c>
+      <c r="P26" t="str">
         <f t="shared" ca="1" si="7"/>
-        <v>25</v>
-      </c>
-      <c r="P26" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v>(1362, 697, 14, 'Personal Injury', 'Open', '2024-11-26', '', 462835.94),</v>
+        <v>(1362, 53, 1422, 'Workers Compensation', 'Open', '2024-11-26', '', 462835.94),</v>
       </c>
     </row>
   </sheetData>
